--- a/SomeBenchmarks/СРЗНАЧ.xlsx
+++ b/SomeBenchmarks/СРЗНАЧ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\DiplomAPI\SomeBenchmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C1C40F-B6D3-4E3B-8FD7-21A7FB3977C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A061D98B-5813-44BC-BEEA-88FD0D27AF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{17BA90DB-EAC0-4426-840B-1E7026F1E105}"/>
   </bookViews>
@@ -203,13 +203,13 @@
     <t>Среднее</t>
   </si>
   <si>
-    <t>Обычный</t>
-  </si>
-  <si>
     <t>Наивный</t>
   </si>
   <si>
-    <t>Обычный 2</t>
+    <t>Скалярный</t>
+  </si>
+  <si>
+    <t>Скалярный опт.</t>
   </si>
 </sst>
 </file>
@@ -321,39 +321,6 @@
       <numFmt numFmtId="165" formatCode="0.00000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.00000"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -394,6 +361,39 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.00000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -653,13 +653,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -849,20 +849,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1234,10 +1220,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -1490,10 +1476,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -1641,10 +1627,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -1836,20 +1822,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -2118,13 +2090,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -2311,20 +2283,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -2546,7 +2504,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -2600,13 +2558,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -2686,7 +2644,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -2740,13 +2698,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -2847,7 +2805,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -2901,13 +2859,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -3397,10 +3355,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -3545,10 +3503,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -3693,10 +3651,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -3763,7 +3721,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000002-C570-4572-9788-2F11B7B68765}"/>
+                        <c16:uniqueId val="{00000001-B5BB-4C0B-8898-736B31593BE3}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -4117,6 +4075,1698 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Мин</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$D$45:$D$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$D$45,'!bench (4)'!$D$47:$D$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.23076923076923</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.526946107784433</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Макс</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$E$45:$E$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$E$45,'!bench (4)'!$E$47:$E$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.9073001158748557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.178571428571429</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.5530035335689059</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.5105672969966637</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.05923836389281</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.01%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$F$45:$F$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$F$45,'!bench (4)'!$F$47:$F$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20.437037037037037</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.223076923076924</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.491332934847581</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.590000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45.983333333333341</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.1%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$G$45:$G$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$G$45,'!bench (4)'!$G$47:$G$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20.444444444444443</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.23076923076923</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.235294117647058</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45.245901639344268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$H$45:$H$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$H$45,'!bench (4)'!$H$47:$H$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>20.481481481481481</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.108481563478129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.890804597701148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.376237623762375</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44.596774193548391</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>50%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="#,##0.00" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$I$45:$I$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$I$45,'!bench (4)'!$I$47:$I$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>21.646428571428569</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.960144927536227</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.569711538461537</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.583333333333336</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42.683098591549289</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$J$45:$J$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$J$45,'!bench (4)'!$J$47:$J$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>15.202674227041113</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.329423868312759</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10.045187585438713</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.556189717724095</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27.555902777777778</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$K$45:$K$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$K$45,'!bench (4)'!$K$47:$K$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10.990802075861778</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.885314285714283</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0596807289674111</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.883613301336988</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>24.231906976744185</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench (4)'!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>99.99%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$A$45:$A$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$A$45,'!bench (4)'!$A$47:$A$50)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Скалярный</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Скалярный опт.</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>SSE</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SSE 2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>AVX</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'!bench (4)'!$L$45:$L$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>('!bench (4)'!$L$45,'!bench (4)'!$L$47:$L$50)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.5342675392012417</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.540914285714285</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3950748516254752</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.7508385744234793</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.985761659122014</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-48AA-492A-BDAC-1558DAB5B843}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="629584399"/>
+        <c:axId val="767350911"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="629584399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Название</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" baseline="0"/>
+                  <a:t> алгоритма</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="767350911"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="767350911"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Во сколько раз быстрее</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="629584399"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
     <c:title>
       <c:overlay val="0"/>
       <c:spPr>
@@ -4861,7 +6511,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -5169,7 +6819,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -5476,7 +7126,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -5907,7 +7557,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -6543,612 +8193,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Временное распределение</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'!bench'!$A$32</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>normal          </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'!bench'!$J$1:$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>99%</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99.9%</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99.999%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'!bench'!$J$32:$L$32</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>5.9199999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1336</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.28339999999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C35A-4C0D-8899-477BDE1DDC44}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'!bench'!$A$33</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>iter            </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'!bench'!$J$1:$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>99%</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99.9%</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99.999%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'!bench'!$J$33:$L$33</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>5.8599999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1196</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.25340000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C35A-4C0D-8899-477BDE1DDC44}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'!bench'!$A$34</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>sse v1          </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'!bench'!$J$1:$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>99%</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99.9%</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99.999%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'!bench'!$J$34:$L$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>9.3199999999999991E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.16819999999999996</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.31500000000000006</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C35A-4C0D-8899-477BDE1DDC44}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'!bench'!$A$35</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>sse v2          </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'!bench'!$J$1:$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>99%</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99.9%</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99.999%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'!bench'!$J$35:$L$35</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>4.8599999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>7.1800000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.19600000000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C35A-4C0D-8899-477BDE1DDC44}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'!bench'!$A$36</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>avx h           </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent5"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'!bench'!$J$1:$L$1</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>99%</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99.9%</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99.999%</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'!bench'!$J$36:$L$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>3.7200000000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5.9199999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.20379999999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C35A-4C0D-8899-477BDE1DDC44}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="456592800"/>
-        <c:axId val="456593216"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="456592800"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="456593216"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="456593216"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="0.32000000000000006"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="456592800"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ru-RU"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -7390,13 +8434,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -7720,6 +8764,612 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Временное распределение</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench'!$A$32</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>normal          </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'!bench'!$J$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.999%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'!bench'!$J$32:$L$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5.9199999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1336</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28339999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C35A-4C0D-8899-477BDE1DDC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench'!$A$33</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>iter            </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'!bench'!$J$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.999%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'!bench'!$J$33:$L$33</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5.8599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1196</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25340000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C35A-4C0D-8899-477BDE1DDC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench'!$A$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sse v1          </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'!bench'!$J$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.999%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'!bench'!$J$34:$L$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>9.3199999999999991E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16819999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.31500000000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C35A-4C0D-8899-477BDE1DDC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench'!$A$35</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>sse v2          </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'!bench'!$J$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.999%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'!bench'!$J$35:$L$35</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>4.8599999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1800000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19600000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-C35A-4C0D-8899-477BDE1DDC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'!bench'!$A$36</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>avx h           </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'!bench'!$J$1:$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>99%</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99.9%</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99.999%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'!bench'!$J$36:$L$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3.7200000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.9199999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20379999999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-C35A-4C0D-8899-477BDE1DDC44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="456592800"/>
+        <c:axId val="456593216"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="456592800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="456593216"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="456593216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="0.32000000000000006"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="456592800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -7917,13 +9567,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -8224,7 +9874,7 @@
               <c:layout>
                 <c:manualLayout>
                   <c:x val="0"/>
-                  <c:y val="-3.9978127734033246E-2"/>
+                  <c:y val="-0.10016331291921843"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="ctr"/>
@@ -8242,11 +9892,33 @@
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.0900855790023482E-17"/>
+                  <c:y val="-0.11866542723826189"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-EC09-4207-B30E-B847B0081B9E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-1.0180173383568863E-16"/>
-                  <c:y val="-4.6118401866433366E-2"/>
+                  <c:x val="-1.0180171158004696E-16"/>
+                  <c:y val="-8.3155438903470311E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="ctr"/>
@@ -8392,13 +10064,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -8416,25 +10088,25 @@
             <c:numRef>
               <c:f>'!bench (5)'!$E$2:$E$7</c:f>
               <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>4.5990000000000002</c:v>
+                  <c:v>31650</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.30399999999999999</c:v>
+                  <c:v>36675</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.1520000000000001</c:v>
+                  <c:v>28200</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>106.312</c:v>
+                  <c:v>165050</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2729999999999997</c:v>
+                  <c:v>19200</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.75</c:v>
+                  <c:v>32175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8569,7 +10241,7 @@
         <c:axId val="1668501535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="110"/>
+          <c:max val="170000"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -8619,6 +10291,14 @@
                   <a:rPr lang="ru-RU" baseline="0"/>
                   <a:t> кэшу</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="ru-RU" baseline="0"/>
+                  <a:t>(тыс)</a:t>
+                </a:r>
                 <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:rich>
@@ -8652,7 +10332,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8686,7 +10366,6 @@
         <c:crossAx val="1668505695"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -9011,13 +10690,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -9412,13 +11091,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -9983,13 +11662,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -10137,13 +11816,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -10615,13 +12294,13 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Наивный</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SSE</c:v>
@@ -11084,10 +12763,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -11236,10 +12915,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -11410,10 +13089,10 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Обычный</c:v>
+                  <c:v>Скалярный</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Обычный 2</c:v>
+                  <c:v>Скалярный опт.</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>SSE</c:v>
@@ -11585,10 +13264,10 @@
                     <c:strCache>
                       <c:ptCount val="5"/>
                       <c:pt idx="0">
-                        <c:v>Обычный</c:v>
+                        <c:v>Скалярный</c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v>Обычный 2</c:v>
+                        <c:v>Скалярный опт.</c:v>
                       </c:pt>
                       <c:pt idx="2">
                         <c:v>SSE</c:v>
@@ -11772,20 +13451,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -12424,6 +14089,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors20.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -15210,6 +16915,509 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="341">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15711,7 +17919,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -16216,7 +18424,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -16721,7 +18929,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -17226,7 +19434,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -17729,8 +19937,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style19.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -17934,22 +20142,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -18054,8 +20263,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -18187,19 +20396,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -18232,8 +20442,8 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+<file path=xl/charts/style20.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -18437,23 +20647,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -18558,8 +20767,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -18691,20 +20900,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -22605,14 +24813,14 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>704850</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>157161</xdr:rowOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>33336</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22641,14 +24849,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22677,14 +24885,14 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>70036</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>89085</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>50985</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>433106</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>43142</xdr:rowOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>5042</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22713,14 +24921,14 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>10645</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>20732</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>173132</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22742,6 +24950,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>402742</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>185291</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>168519</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Диаграмма 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42A6FD62-FE22-47D5-8703-CE8107FC2F86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -23041,38 +25285,38 @@
   <autoFilter ref="A1:L35" xr:uid="{0541F17D-05C2-4A76-8324-93867D083F32}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{61943C34-6EFB-4BCA-888A-89C0A3AD588E}" uniqueName="1" name="name" queryTableFieldId="1" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{F325066E-BC6A-4EB6-9D94-50CFA9455FE6}" uniqueName="2" name="Среднее" queryTableFieldId="2" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{EE0C8C77-9C3B-415E-8F36-E1AB9CDF02E4}" uniqueName="3" name="Среднее отклонение" queryTableFieldId="3" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C3ECA0BB-F633-41BF-A9F0-8BEF86AC205A}" uniqueName="4" name="Мин" queryTableFieldId="4" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{33B62EAD-2CD7-44E7-837A-C3D3BFF573E9}" uniqueName="5" name="Макс" queryTableFieldId="5" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{04F3ED80-18CC-4E43-BB78-3B1A07CBCFF7}" uniqueName="6" name="0.01%" queryTableFieldId="6" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{64CB85BC-D387-4E7A-9D0A-D78E1A0F7B33}" uniqueName="7" name="0.1%" queryTableFieldId="7" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{B98AE064-4378-4EFB-98C9-5632601C983D}" uniqueName="8" name="1%" queryTableFieldId="8" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{FCE1E06F-8041-4356-AAF5-30FA8C208829}" uniqueName="9" name="50%" queryTableFieldId="9" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{E6C4EC49-BE92-450C-96C2-810F2F5D6E46}" uniqueName="10" name="99%" queryTableFieldId="10" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{DE25D263-BBAB-4FFA-B0BB-9948CC65838D}" uniqueName="11" name="99.9%" queryTableFieldId="11" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{6AADA61C-6759-4DB2-B9EA-FE21119E467C}" uniqueName="12" name="99.99%" queryTableFieldId="12" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{F325066E-BC6A-4EB6-9D94-50CFA9455FE6}" uniqueName="2" name="Среднее" queryTableFieldId="2" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{EE0C8C77-9C3B-415E-8F36-E1AB9CDF02E4}" uniqueName="3" name="Среднее отклонение" queryTableFieldId="3" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{C3ECA0BB-F633-41BF-A9F0-8BEF86AC205A}" uniqueName="4" name="Мин" queryTableFieldId="4" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{33B62EAD-2CD7-44E7-837A-C3D3BFF573E9}" uniqueName="5" name="Макс" queryTableFieldId="5" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{04F3ED80-18CC-4E43-BB78-3B1A07CBCFF7}" uniqueName="6" name="0.01%" queryTableFieldId="6" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{64CB85BC-D387-4E7A-9D0A-D78E1A0F7B33}" uniqueName="7" name="0.1%" queryTableFieldId="7" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{B98AE064-4378-4EFB-98C9-5632601C983D}" uniqueName="8" name="1%" queryTableFieldId="8" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{FCE1E06F-8041-4356-AAF5-30FA8C208829}" uniqueName="9" name="50%" queryTableFieldId="9" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{E6C4EC49-BE92-450C-96C2-810F2F5D6E46}" uniqueName="10" name="99%" queryTableFieldId="10" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{DE25D263-BBAB-4FFA-B0BB-9948CC65838D}" uniqueName="11" name="99.9%" queryTableFieldId="11" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{6AADA61C-6759-4DB2-B9EA-FE21119E467C}" uniqueName="12" name="99.99%" queryTableFieldId="12" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EA6A69C6-70E6-456B-BD2E-93F78213020D}" name="bench__3" displayName="bench__3" ref="A1:L35" tableType="queryTable" totalsRowShown="0" headerRowDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EA6A69C6-70E6-456B-BD2E-93F78213020D}" name="bench__3" displayName="bench__3" ref="A1:L35" tableType="queryTable" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="A1:L35" xr:uid="{EA6A69C6-70E6-456B-BD2E-93F78213020D}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{528A0E9A-8905-4694-95A7-AEFE9DE57EE9}" uniqueName="1" name="Algorithm       " queryTableFieldId="1" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{687BCE85-0B3B-433E-8E41-D1E342DB6523}" uniqueName="2" name="        Avg " queryTableFieldId="2" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{0C5CFAC3-9D81-4CDD-A138-6D24C07DD630}" uniqueName="3" name="     StdDev " queryTableFieldId="3" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{C9D40B0F-8566-454C-A509-537A31E456B7}" uniqueName="4" name="        Min " queryTableFieldId="4" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{7DB63788-72EA-461A-98B6-1FFBD64C63C7}" uniqueName="5" name="        Max " queryTableFieldId="5" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{CAF6E545-2E9E-4353-AE1A-D8AB5EDD3625}" uniqueName="6" name="    p0.001% " queryTableFieldId="6" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{51E7AF4C-0812-43DD-A18A-622C39FF1FB3}" uniqueName="7" name="      p0.1% " queryTableFieldId="7" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{3FF1168A-1EA2-442C-8D1F-70E4555E1A6B}" uniqueName="8" name="        p1% " queryTableFieldId="8" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{E615164D-51EA-4B5A-B548-CB0C256DFEAF}" uniqueName="9" name="       p50% " queryTableFieldId="9" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{B12093D0-E25F-44AC-A483-6494F9104F4D}" uniqueName="10" name="       p99% " queryTableFieldId="10" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{FDD51BAD-4E1A-4102-A5F1-FB5AC62B0BF4}" uniqueName="11" name="     p99.9% " queryTableFieldId="11" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{8FE203E8-E5F2-4D66-A9C5-22EB0CA02117}" uniqueName="12" name="   p99.999%" queryTableFieldId="12" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{528A0E9A-8905-4694-95A7-AEFE9DE57EE9}" uniqueName="1" name="Algorithm       " queryTableFieldId="1" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{687BCE85-0B3B-433E-8E41-D1E342DB6523}" uniqueName="2" name="        Avg " queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{0C5CFAC3-9D81-4CDD-A138-6D24C07DD630}" uniqueName="3" name="     StdDev " queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{C9D40B0F-8566-454C-A509-537A31E456B7}" uniqueName="4" name="        Min " queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{7DB63788-72EA-461A-98B6-1FFBD64C63C7}" uniqueName="5" name="        Max " queryTableFieldId="5" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{CAF6E545-2E9E-4353-AE1A-D8AB5EDD3625}" uniqueName="6" name="    p0.001% " queryTableFieldId="6" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{51E7AF4C-0812-43DD-A18A-622C39FF1FB3}" uniqueName="7" name="      p0.1% " queryTableFieldId="7" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{3FF1168A-1EA2-442C-8D1F-70E4555E1A6B}" uniqueName="8" name="        p1% " queryTableFieldId="8" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{E615164D-51EA-4B5A-B548-CB0C256DFEAF}" uniqueName="9" name="       p50% " queryTableFieldId="9" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{B12093D0-E25F-44AC-A483-6494F9104F4D}" uniqueName="10" name="       p99% " queryTableFieldId="10" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{FDD51BAD-4E1A-4102-A5F1-FB5AC62B0BF4}" uniqueName="11" name="     p99.9% " queryTableFieldId="11" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{8FE203E8-E5F2-4D66-A9C5-22EB0CA02117}" uniqueName="12" name="   p99.999%" queryTableFieldId="12" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -23082,18 +25326,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{045CAE21-E4D9-49DE-BBCE-C12DFA3FDDCA}" name="bench" displayName="bench" ref="A1:L30" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:L30" xr:uid="{045CAE21-E4D9-49DE-BBCE-C12DFA3FDDCA}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{0F36093B-02CC-462A-A40D-08DF9B226316}" uniqueName="1" name="Название" queryTableFieldId="1" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{082B2C1D-D0B9-4100-933F-C9C88017AD51}" uniqueName="2" name="Среднее время" queryTableFieldId="2" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{CF09B150-4429-45B0-8047-93E3B1D3E12A}" uniqueName="3" name="Отклонение" queryTableFieldId="3" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{7EBE48DE-EF61-432D-9065-16B4D2DA4708}" uniqueName="4" name="Мин" queryTableFieldId="4" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{7DA36E49-406A-4751-8424-ED392CF5F40D}" uniqueName="5" name="Макс" queryTableFieldId="5" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{D544150B-FC18-401D-9EC2-0E5BF5890B81}" uniqueName="6" name="0.001%" queryTableFieldId="6" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{3B88069A-7730-4CB5-BA24-25FFF3B0D88C}" uniqueName="7" name="0.1%" queryTableFieldId="7" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{3A85081F-7758-4D9A-A562-D9C32CE11A6D}" uniqueName="8" name="1%" queryTableFieldId="8" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{685F835B-F793-44E4-B4F2-8B5C33C83319}" uniqueName="9" name="50%" queryTableFieldId="9" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{96F4E968-2575-4D2F-962C-867A284B65E4}" uniqueName="10" name="99%" queryTableFieldId="10" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{4E023C2C-1010-4059-8CAE-CB6D547CDB2F}" uniqueName="11" name="99.9%" queryTableFieldId="11" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{65826AF4-AAC3-4B5A-A685-F79290F78C6B}" uniqueName="12" name="99.999%" queryTableFieldId="12" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{0F36093B-02CC-462A-A40D-08DF9B226316}" uniqueName="1" name="Название" queryTableFieldId="1" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{082B2C1D-D0B9-4100-933F-C9C88017AD51}" uniqueName="2" name="Среднее время" queryTableFieldId="2" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{CF09B150-4429-45B0-8047-93E3B1D3E12A}" uniqueName="3" name="Отклонение" queryTableFieldId="3" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{7EBE48DE-EF61-432D-9065-16B4D2DA4708}" uniqueName="4" name="Мин" queryTableFieldId="4" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{7DA36E49-406A-4751-8424-ED392CF5F40D}" uniqueName="5" name="Макс" queryTableFieldId="5" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{D544150B-FC18-401D-9EC2-0E5BF5890B81}" uniqueName="6" name="0.001%" queryTableFieldId="6" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{3B88069A-7730-4CB5-BA24-25FFF3B0D88C}" uniqueName="7" name="0.1%" queryTableFieldId="7" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{3A85081F-7758-4D9A-A562-D9C32CE11A6D}" uniqueName="8" name="1%" queryTableFieldId="8" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{685F835B-F793-44E4-B4F2-8B5C33C83319}" uniqueName="9" name="50%" queryTableFieldId="9" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{96F4E968-2575-4D2F-962C-867A284B65E4}" uniqueName="10" name="99%" queryTableFieldId="10" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{4E023C2C-1010-4059-8CAE-CB6D547CDB2F}" uniqueName="11" name="99.9%" queryTableFieldId="11" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{65826AF4-AAC3-4B5A-A685-F79290F78C6B}" uniqueName="12" name="99.999%" queryTableFieldId="12" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -23400,7 +25644,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23423,7 +25669,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="6">
         <v>3.331</v>
@@ -23434,8 +25680,8 @@
       <c r="D2" s="9">
         <v>2753</v>
       </c>
-      <c r="E2" s="6">
-        <v>4.5990000000000002</v>
+      <c r="E2" s="9">
+        <v>31650</v>
       </c>
       <c r="F2" s="9">
         <v>2668</v>
@@ -23443,7 +25689,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" s="6">
         <v>3.39</v>
@@ -23454,8 +25700,8 @@
       <c r="D3" s="9">
         <v>48304</v>
       </c>
-      <c r="E3" s="6">
-        <v>0.30399999999999999</v>
+      <c r="E3" s="9">
+        <v>36675</v>
       </c>
       <c r="F3" s="9">
         <v>44</v>
@@ -23474,8 +25720,8 @@
       <c r="D4" s="9">
         <v>2717</v>
       </c>
-      <c r="E4" s="6">
-        <v>4.1520000000000001</v>
+      <c r="E4" s="9">
+        <v>28200</v>
       </c>
       <c r="F4" s="9">
         <v>3098</v>
@@ -23494,8 +25740,8 @@
       <c r="D5" s="9">
         <v>621</v>
       </c>
-      <c r="E5" s="6">
-        <v>106.312</v>
+      <c r="E5" s="9">
+        <v>165050</v>
       </c>
       <c r="F5" s="9">
         <v>2608</v>
@@ -23514,8 +25760,8 @@
       <c r="D6" s="9">
         <v>1056</v>
       </c>
-      <c r="E6" s="6">
-        <v>7.2729999999999997</v>
+      <c r="E6" s="9">
+        <v>19200</v>
       </c>
       <c r="F6" s="9">
         <v>1</v>
@@ -23534,8 +25780,8 @@
       <c r="D7" s="9">
         <v>520</v>
       </c>
-      <c r="E7" s="6">
-        <v>24.75</v>
+      <c r="E7" s="9">
+        <v>32175</v>
       </c>
       <c r="F7" s="9">
         <v>1</v>
@@ -23553,8 +25799,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -24881,99 +27127,99 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="4">
-        <f>AVERAGE(B2,B9,B16,B23,B30)</f>
+        <f t="shared" ref="B37:L37" si="0">AVERAGE(B2,B9,B16,B23,B30)</f>
         <v>3.1139999999999994E-2</v>
       </c>
       <c r="C37">
-        <f>AVERAGE(C2,C9,C16,C23,C30)</f>
+        <f t="shared" si="0"/>
         <v>6.0219999999999996E-3</v>
       </c>
       <c r="D37">
-        <f>AVERAGE(D2,D9,D16,D23,D30)</f>
+        <f t="shared" si="0"/>
         <v>2.7000000000000003E-2</v>
       </c>
       <c r="E37">
-        <f>AVERAGE(E2,E9,E16,E23,E30)</f>
+        <f t="shared" si="0"/>
         <v>0.1726</v>
       </c>
       <c r="F37">
-        <f>AVERAGE(F2,F9,F16,F23,F30)</f>
+        <f t="shared" si="0"/>
         <v>2.7000000000000003E-2</v>
       </c>
       <c r="G37">
-        <f>AVERAGE(G2,G9,G16,G23,G30)</f>
+        <f t="shared" si="0"/>
         <v>2.7000000000000003E-2</v>
       </c>
       <c r="H37">
-        <f>AVERAGE(H2,H9,H16,H23,H30)</f>
+        <f t="shared" si="0"/>
         <v>2.7000000000000003E-2</v>
       </c>
       <c r="I37">
-        <f>AVERAGE(I2,I9,I16,I23,I30)</f>
+        <f t="shared" si="0"/>
         <v>2.8000000000000004E-2</v>
       </c>
       <c r="J37">
-        <f>AVERAGE(J2,J9,J16,J23,J30)</f>
+        <f t="shared" si="0"/>
         <v>5.2201999999999991E-2</v>
       </c>
       <c r="K37">
-        <f>AVERAGE(K2,K9,K16,K23,K30)</f>
+        <f t="shared" si="0"/>
         <v>9.4803999999999999E-2</v>
       </c>
       <c r="L37">
-        <f>AVERAGE(L2,L9,L16,L23,L30)</f>
+        <f t="shared" si="0"/>
         <v>0.175122</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38">
-        <f>AVERAGE(B3,B10,B17,B24,B31)</f>
+        <f t="shared" ref="B38:L38" si="1">AVERAGE(B3,B10,B17,B24,B31)</f>
         <v>0.621726</v>
       </c>
       <c r="C38">
-        <f>AVERAGE(C3,C10,C17,C24,C31)</f>
+        <f t="shared" si="1"/>
         <v>6.9935999999999998E-2</v>
       </c>
       <c r="D38">
-        <f>AVERAGE(D3,D10,D17,D24,D31)</f>
+        <f t="shared" si="1"/>
         <v>0.55200000000000005</v>
       </c>
       <c r="E38">
-        <f>AVERAGE(E3,E10,E17,E24,E31)</f>
+        <f t="shared" si="1"/>
         <v>1.7100000000000002</v>
       </c>
       <c r="F38">
-        <f>AVERAGE(F3,F10,F17,F24,F31)</f>
+        <f t="shared" si="1"/>
         <v>0.55180000000000007</v>
       </c>
       <c r="G38">
-        <f>AVERAGE(G3,G10,G17,G24,G31)</f>
+        <f t="shared" si="1"/>
         <v>0.55200000000000005</v>
       </c>
       <c r="H38">
-        <f>AVERAGE(H3,H10,H17,H24,H31)</f>
+        <f t="shared" si="1"/>
         <v>0.55300000000000005</v>
       </c>
       <c r="I38">
-        <f>AVERAGE(I3,I10,I17,I24,I31)</f>
+        <f t="shared" si="1"/>
         <v>0.60609999999999997</v>
       </c>
       <c r="J38">
-        <f>AVERAGE(J3,J10,J17,J24,J31)</f>
+        <f t="shared" si="1"/>
         <v>0.79361000000000004</v>
       </c>
       <c r="K38">
-        <f>AVERAGE(K3,K10,K17,K24,K31)</f>
+        <f t="shared" si="1"/>
         <v>1.0419719999999999</v>
       </c>
       <c r="L38">
-        <f>AVERAGE(L3,L10,L17,L24,L31)</f>
+        <f t="shared" si="1"/>
         <v>1.6696599999999999</v>
       </c>
     </row>
@@ -24982,47 +27228,47 @@
         <v>48</v>
       </c>
       <c r="B39">
-        <f>AVERAGE(B4,B11,B18,B25,B32)</f>
+        <f t="shared" ref="B39:L39" si="2">AVERAGE(B4,B11,B18,B25,B32)</f>
         <v>3.0237999999999998E-2</v>
       </c>
       <c r="C39">
-        <f>AVERAGE(C4,C11,C18,C25,C32)</f>
+        <f t="shared" si="2"/>
         <v>5.5500000000000002E-3</v>
       </c>
       <c r="D39">
-        <f>AVERAGE(D4,D11,D18,D25,D32)</f>
+        <f t="shared" si="2"/>
         <v>2.6000000000000002E-2</v>
       </c>
       <c r="E39">
-        <f>AVERAGE(E4,E11,E18,E25,E32)</f>
+        <f t="shared" si="2"/>
         <v>0.16800000000000001</v>
       </c>
       <c r="F39">
-        <f>AVERAGE(F4,F11,F18,F25,F32)</f>
+        <f t="shared" si="2"/>
         <v>2.6000000000000002E-2</v>
       </c>
       <c r="G39">
-        <f>AVERAGE(G4,G11,G18,G25,G32)</f>
+        <f t="shared" si="2"/>
         <v>2.6000000000000002E-2</v>
       </c>
       <c r="H39">
-        <f>AVERAGE(H4,H11,H18,H25,H32)</f>
+        <f t="shared" si="2"/>
         <v>2.6197999999999999E-2</v>
       </c>
       <c r="I39">
-        <f>AVERAGE(I4,I11,I18,I25,I32)</f>
+        <f t="shared" si="2"/>
         <v>2.7600000000000003E-2</v>
       </c>
       <c r="J39">
-        <f>AVERAGE(J4,J11,J18,J25,J32)</f>
+        <f t="shared" si="2"/>
         <v>4.8599999999999997E-2</v>
       </c>
       <c r="K39">
-        <f>AVERAGE(K4,K11,K18,K25,K32)</f>
+        <f t="shared" si="2"/>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="L39">
-        <f>AVERAGE(L4,L11,L18,L25,L32)</f>
+        <f t="shared" si="2"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -25031,47 +27277,47 @@
         <v>42</v>
       </c>
       <c r="B40">
-        <f>AVERAGE(B5,B12,B19,B26,B33)</f>
+        <f t="shared" ref="B40:L40" si="3">AVERAGE(B5,B12,B19,B26,B33)</f>
         <v>4.4041999999999998E-2</v>
       </c>
       <c r="C40">
-        <f>AVERAGE(C5,C12,C19,C26,C33)</f>
+        <f t="shared" si="3"/>
         <v>1.0772E-2</v>
       </c>
       <c r="D40">
-        <f>AVERAGE(D5,D12,D19,D26,D33)</f>
+        <f t="shared" si="3"/>
         <v>3.3399999999999999E-2</v>
       </c>
       <c r="E40">
-        <f>AVERAGE(E5,E12,E19,E26,E33)</f>
+        <f t="shared" si="3"/>
         <v>0.22639999999999999</v>
       </c>
       <c r="F40">
-        <f>AVERAGE(F5,F12,F19,F26,F33)</f>
+        <f t="shared" si="3"/>
         <v>3.3460000000000004E-2</v>
       </c>
       <c r="G40">
-        <f>AVERAGE(G5,G12,G19,G26,G33)</f>
+        <f t="shared" si="3"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="H40">
-        <f>AVERAGE(H5,H12,H19,H26,H33)</f>
+        <f t="shared" si="3"/>
         <v>3.4800000000000005E-2</v>
       </c>
       <c r="I40">
-        <f>AVERAGE(I5,I12,I19,I26,I33)</f>
+        <f t="shared" si="3"/>
         <v>4.1600000000000005E-2</v>
       </c>
       <c r="J40">
-        <f>AVERAGE(J5,J12,J19,J26,J33)</f>
+        <f t="shared" si="3"/>
         <v>7.9003999999999991E-2</v>
       </c>
       <c r="K40">
-        <f>AVERAGE(K5,K12,K19,K26,K33)</f>
+        <f t="shared" si="3"/>
         <v>0.115012</v>
       </c>
       <c r="L40">
-        <f>AVERAGE(L5,L12,L19,L26,L33)</f>
+        <f t="shared" si="3"/>
         <v>0.22578000000000001</v>
       </c>
     </row>
@@ -25080,47 +27326,47 @@
         <v>43</v>
       </c>
       <c r="B41">
-        <f>AVERAGE(B6,B13,B20,B27,B34)</f>
+        <f t="shared" ref="B41:L41" si="4">AVERAGE(B6,B13,B20,B27,B34)</f>
         <v>2.4496E-2</v>
       </c>
       <c r="C41">
-        <f>AVERAGE(C6,C13,C20,C27,C34)</f>
+        <f t="shared" si="4"/>
         <v>5.2720000000000006E-3</v>
       </c>
       <c r="D41">
-        <f>AVERAGE(D6,D13,D20,D27,D34)</f>
+        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
       <c r="E41">
-        <f>AVERAGE(E6,E13,E20,E27,E34)</f>
+        <f t="shared" si="4"/>
         <v>0.17980000000000002</v>
       </c>
       <c r="F41">
-        <f>AVERAGE(F6,F13,F20,F27,F34)</f>
+        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
       <c r="G41">
-        <f>AVERAGE(G6,G13,G20,G27,G34)</f>
+        <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
       <c r="H41">
-        <f>AVERAGE(H6,H13,H20,H27,H34)</f>
+        <f t="shared" si="4"/>
         <v>2.0200000000000003E-2</v>
       </c>
       <c r="I41">
-        <f>AVERAGE(I6,I13,I20,I27,I34)</f>
+        <f t="shared" si="4"/>
         <v>2.2799999999999997E-2</v>
       </c>
       <c r="J41">
-        <f>AVERAGE(J6,J13,J20,J27,J34)</f>
+        <f t="shared" si="4"/>
         <v>4.5204000000000001E-2</v>
       </c>
       <c r="K41">
-        <f>AVERAGE(K6,K13,K20,K27,K34)</f>
+        <f t="shared" si="4"/>
         <v>7.0008000000000001E-2</v>
       </c>
       <c r="L41">
-        <f>AVERAGE(L6,L13,L20,L27,L34)</f>
+        <f t="shared" si="4"/>
         <v>0.1908</v>
       </c>
     </row>
@@ -25129,48 +27375,86 @@
         <v>44</v>
       </c>
       <c r="B42">
-        <f>AVERAGE(B7,B14,B21,B28,B35)</f>
+        <f t="shared" ref="B42:L42" si="5">AVERAGE(B7,B14,B21,B28,B35)</f>
         <v>1.4638000000000002E-2</v>
       </c>
       <c r="C42">
-        <f>AVERAGE(C7,C14,C21,C28,C35)</f>
+        <f t="shared" si="5"/>
         <v>3.2599999999999999E-3</v>
       </c>
       <c r="D42">
-        <f>AVERAGE(D7,D14,D21,D28,D35)</f>
+        <f t="shared" si="5"/>
         <v>1.2E-2</v>
       </c>
       <c r="E42">
-        <f>AVERAGE(E7,E14,E21,E28,E35)</f>
+        <f t="shared" si="5"/>
         <v>0.14179999999999998</v>
       </c>
       <c r="F42">
-        <f>AVERAGE(F7,F14,F21,F28,F35)</f>
+        <f t="shared" si="5"/>
         <v>1.2E-2</v>
       </c>
       <c r="G42">
-        <f>AVERAGE(G7,G14,G21,G28,G35)</f>
+        <f t="shared" si="5"/>
         <v>1.2199999999999999E-2</v>
       </c>
       <c r="H42">
-        <f>AVERAGE(H7,H14,H21,H28,H35)</f>
+        <f t="shared" si="5"/>
         <v>1.24E-2</v>
       </c>
       <c r="I42">
-        <f>AVERAGE(I7,I14,I21,I28,I35)</f>
+        <f t="shared" si="5"/>
         <v>1.4200000000000001E-2</v>
       </c>
       <c r="J42">
-        <f>AVERAGE(J7,J14,J21,J28,J35)</f>
+        <f t="shared" si="5"/>
         <v>2.8800000000000003E-2</v>
       </c>
       <c r="K42">
-        <f>AVERAGE(K7,K14,K21,K28,K35)</f>
+        <f t="shared" si="5"/>
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="L42" s="4">
-        <f>AVERAGE(L7,L14,L21,L28,L35)</f>
+        <f t="shared" si="5"/>
         <v>0.15198399999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <f>MAX(D37:D42)</f>
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="E43">
+        <f t="shared" ref="E43:L43" si="6">MAX(E37:E42)</f>
+        <v>1.7100000000000002</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="6"/>
+        <v>0.55180000000000007</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="6"/>
+        <v>0.55200000000000005</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="6"/>
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="6"/>
+        <v>0.60609999999999997</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="6"/>
+        <v>0.79361000000000004</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="6"/>
+        <v>1.0419719999999999</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="6"/>
+        <v>1.6696599999999999</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -25181,65 +27465,389 @@
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>A37</f>
-        <v>Обычный</v>
+        <v>Скалярный</v>
       </c>
       <c r="B45">
-        <f>C30/B30*100</f>
+        <f t="shared" ref="B45:B50" si="7">C30/B30*100</f>
         <v>23.506866815713831</v>
+      </c>
+      <c r="D45" s="6">
+        <f>D43/D37</f>
+        <v>20.444444444444443</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" ref="E45:L45" si="8">E43/E37</f>
+        <v>9.9073001158748557</v>
+      </c>
+      <c r="F45" s="6">
+        <f t="shared" si="8"/>
+        <v>20.437037037037037</v>
+      </c>
+      <c r="G45" s="6">
+        <f t="shared" si="8"/>
+        <v>20.444444444444443</v>
+      </c>
+      <c r="H45" s="6">
+        <f t="shared" si="8"/>
+        <v>20.481481481481481</v>
+      </c>
+      <c r="I45" s="6">
+        <f t="shared" si="8"/>
+        <v>21.646428571428569</v>
+      </c>
+      <c r="J45" s="6">
+        <f t="shared" si="8"/>
+        <v>15.202674227041113</v>
+      </c>
+      <c r="K45" s="6">
+        <f t="shared" si="8"/>
+        <v>10.990802075861778</v>
+      </c>
+      <c r="L45" s="6">
+        <f t="shared" si="8"/>
+        <v>9.5342675392012417</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <f t="shared" ref="A46:A50" si="0">A38</f>
+        <f t="shared" ref="A46:A50" si="9">A38</f>
         <v>Наивный</v>
       </c>
       <c r="B46">
-        <f>C31/B31*100</f>
+        <f t="shared" si="7"/>
         <v>11.508955485733424</v>
+      </c>
+      <c r="D46" s="6">
+        <f>D43/D38</f>
+        <v>1</v>
+      </c>
+      <c r="E46" s="6">
+        <f t="shared" ref="E46:L46" si="10">E43/E38</f>
+        <v>1</v>
+      </c>
+      <c r="F46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="G46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="J46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="K46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="L46" s="6">
+        <f t="shared" si="10"/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <f t="shared" si="0"/>
-        <v>Обычный 2</v>
+        <f t="shared" si="9"/>
+        <v>Скалярный опт.</v>
       </c>
       <c r="B47">
-        <f>C32/B32*100</f>
+        <f t="shared" si="7"/>
         <v>19.167217448777262</v>
+      </c>
+      <c r="D47" s="6">
+        <f>D43/D39</f>
+        <v>21.23076923076923</v>
+      </c>
+      <c r="E47" s="6">
+        <f t="shared" ref="E47:L47" si="11">E43/E39</f>
+        <v>10.178571428571429</v>
+      </c>
+      <c r="F47" s="6">
+        <f t="shared" si="11"/>
+        <v>21.223076923076924</v>
+      </c>
+      <c r="G47" s="6">
+        <f t="shared" si="11"/>
+        <v>21.23076923076923</v>
+      </c>
+      <c r="H47" s="6">
+        <f t="shared" si="11"/>
+        <v>21.108481563478129</v>
+      </c>
+      <c r="I47" s="6">
+        <f t="shared" si="11"/>
+        <v>21.960144927536227</v>
+      </c>
+      <c r="J47" s="6">
+        <f t="shared" si="11"/>
+        <v>16.329423868312759</v>
+      </c>
+      <c r="K47" s="6">
+        <f t="shared" si="11"/>
+        <v>14.885314285714283</v>
+      </c>
+      <c r="L47" s="6">
+        <f t="shared" si="11"/>
+        <v>9.540914285714285</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>SSE</v>
       </c>
       <c r="B48">
-        <f>C33/B33*100</f>
+        <f t="shared" si="7"/>
         <v>24.095840867992766</v>
       </c>
+      <c r="D48" s="6">
+        <f>D43/D40</f>
+        <v>16.526946107784433</v>
+      </c>
+      <c r="E48" s="6">
+        <f t="shared" ref="E48:L48" si="12">E43/E40</f>
+        <v>7.5530035335689059</v>
+      </c>
+      <c r="F48" s="6">
+        <f t="shared" si="12"/>
+        <v>16.491332934847581</v>
+      </c>
+      <c r="G48" s="6">
+        <f t="shared" si="12"/>
+        <v>16.235294117647058</v>
+      </c>
+      <c r="H48" s="6">
+        <f t="shared" si="12"/>
+        <v>15.890804597701148</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="12"/>
+        <v>14.569711538461537</v>
+      </c>
+      <c r="J48" s="6">
+        <f t="shared" si="12"/>
+        <v>10.045187585438713</v>
+      </c>
+      <c r="K48" s="6">
+        <f t="shared" si="12"/>
+        <v>9.0596807289674111</v>
+      </c>
+      <c r="L48" s="6">
+        <f t="shared" si="12"/>
+        <v>7.3950748516254752</v>
+      </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>SSE 2</v>
       </c>
       <c r="B49">
         <f>C34/B34*100</f>
         <v>24.096385542168676</v>
       </c>
+      <c r="D49" s="6">
+        <f>D43/D41</f>
+        <v>27.6</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" ref="E49:L49" si="13">E43/E41</f>
+        <v>9.5105672969966637</v>
+      </c>
+      <c r="F49" s="6">
+        <f t="shared" si="13"/>
+        <v>27.590000000000003</v>
+      </c>
+      <c r="G49" s="6">
+        <f t="shared" si="13"/>
+        <v>27.6</v>
+      </c>
+      <c r="H49" s="6">
+        <f t="shared" si="13"/>
+        <v>27.376237623762375</v>
+      </c>
+      <c r="I49" s="6">
+        <f t="shared" si="13"/>
+        <v>26.583333333333336</v>
+      </c>
+      <c r="J49" s="6">
+        <f t="shared" si="13"/>
+        <v>17.556189717724095</v>
+      </c>
+      <c r="K49" s="6">
+        <f t="shared" si="13"/>
+        <v>14.883613301336988</v>
+      </c>
+      <c r="L49" s="6">
+        <f t="shared" si="13"/>
+        <v>8.7508385744234793</v>
+      </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>AVX</v>
       </c>
       <c r="B50">
-        <f>C35/B35*100</f>
+        <f t="shared" si="7"/>
         <v>20.917678812415655</v>
+      </c>
+      <c r="D50" s="6">
+        <f>D43/D42</f>
+        <v>46</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" ref="E50:L50" si="14">E43/E42</f>
+        <v>12.05923836389281</v>
+      </c>
+      <c r="F50" s="6">
+        <f t="shared" si="14"/>
+        <v>45.983333333333341</v>
+      </c>
+      <c r="G50" s="6">
+        <f t="shared" si="14"/>
+        <v>45.245901639344268</v>
+      </c>
+      <c r="H50" s="6">
+        <f t="shared" si="14"/>
+        <v>44.596774193548391</v>
+      </c>
+      <c r="I50" s="6">
+        <f t="shared" si="14"/>
+        <v>42.683098591549289</v>
+      </c>
+      <c r="J50" s="6">
+        <f t="shared" si="14"/>
+        <v>27.555902777777778</v>
+      </c>
+      <c r="K50" s="6">
+        <f t="shared" si="14"/>
+        <v>24.231906976744185</v>
+      </c>
+      <c r="L50" s="6">
+        <f t="shared" si="14"/>
+        <v>10.985761659122014</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B37:B42">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37:C42">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D37:D42">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:E42">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37:F42">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G42">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37:H42">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I37:I42">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37:J42">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:K42">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -25251,7 +27859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C37:C42">
+  <conditionalFormatting sqref="L37:L42">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -25263,7 +27871,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:D42">
+  <conditionalFormatting sqref="B45:B50">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -25275,19 +27883,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E37:E42">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F37:F42">
+  <conditionalFormatting sqref="D37:D42">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -25299,87 +27895,75 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G37:G42">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H42">
+  <conditionalFormatting sqref="D45:L50">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I37:I42">
+  <conditionalFormatting sqref="E45:E50">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J37:J42">
+  <conditionalFormatting sqref="J45:J50">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K37:K42">
+  <conditionalFormatting sqref="K45:K50">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L37:L42">
+  <conditionalFormatting sqref="L45:L50">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B50">
+  <conditionalFormatting sqref="I45:I50">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>

--- a/SomeBenchmarks/СРЗНАЧ.xlsx
+++ b/SomeBenchmarks/СРЗНАЧ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\DiplomAPI\SomeBenchmarks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A061D98B-5813-44BC-BEEA-88FD0D27AF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A174698B-B51B-4A59-BCAD-C549370B0B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{17BA90DB-EAC0-4426-840B-1E7026F1E105}"/>
+    <workbookView xWindow="-16200" yWindow="-4635" windowWidth="16305" windowHeight="11295" activeTab="1" xr2:uid="{17BA90DB-EAC0-4426-840B-1E7026F1E105}"/>
   </bookViews>
   <sheets>
     <sheet name="!bench (5)" sheetId="7" r:id="rId1"/>
@@ -188,9 +188,6 @@
     <t>99.99%</t>
   </si>
   <si>
-    <t>Среднее отклонение</t>
-  </si>
-  <si>
     <t>SSE</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>Скалярный опт.</t>
+  </si>
+  <si>
+    <t>Ср.Отклонение</t>
   </si>
 </sst>
 </file>
@@ -3721,7 +3721,7 @@
                     <c:extLst>
                       <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                       <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                        <c16:uniqueId val="{00000001-B5BB-4C0B-8898-736B31593BE3}"/>
+                        <c16:uniqueId val="{00000000-3EAB-4E7A-B2CE-66525445F332}"/>
                       </c:ext>
                     </c:extLst>
                   </c15:dLbl>
@@ -4116,7 +4116,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -4265,7 +4265,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -4415,7 +4415,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -4565,7 +4565,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -4715,7 +4715,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -4865,7 +4865,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -5016,7 +5016,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -5167,7 +5167,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -5318,7 +5318,7 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
@@ -25286,7 +25286,7 @@
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{61943C34-6EFB-4BCA-888A-89C0A3AD588E}" uniqueName="1" name="name" queryTableFieldId="1" dataDxfId="36"/>
     <tableColumn id="2" xr3:uid="{F325066E-BC6A-4EB6-9D94-50CFA9455FE6}" uniqueName="2" name="Среднее" queryTableFieldId="2" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{EE0C8C77-9C3B-415E-8F36-E1AB9CDF02E4}" uniqueName="3" name="Среднее отклонение" queryTableFieldId="3" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{EE0C8C77-9C3B-415E-8F36-E1AB9CDF02E4}" uniqueName="3" name="Ср.Отклонение" queryTableFieldId="3" dataDxfId="34"/>
     <tableColumn id="4" xr3:uid="{C3ECA0BB-F633-41BF-A9F0-8BEF86AC205A}" uniqueName="4" name="Мин" queryTableFieldId="4" dataDxfId="33"/>
     <tableColumn id="5" xr3:uid="{33B62EAD-2CD7-44E7-837A-C3D3BFF573E9}" uniqueName="5" name="Макс" queryTableFieldId="5" dataDxfId="32"/>
     <tableColumn id="6" xr3:uid="{04F3ED80-18CC-4E43-BB78-3B1A07CBCFF7}" uniqueName="6" name="0.01%" queryTableFieldId="6" dataDxfId="31"/>
@@ -25669,7 +25669,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="6">
         <v>3.331</v>
@@ -25689,7 +25689,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" s="6">
         <v>3.39</v>
@@ -25709,7 +25709,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="6">
         <v>3.38</v>
@@ -25729,7 +25729,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="6">
         <v>1.9530000000000001</v>
@@ -25749,7 +25749,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="6">
         <v>4.0819999999999999</v>
@@ -25769,7 +25769,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B7" s="6">
         <v>3.242</v>
@@ -25808,10 +25808,10 @@
         <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
@@ -27127,7 +27127,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="4">
         <f t="shared" ref="B37:L37" si="0">AVERAGE(B2,B9,B16,B23,B30)</f>
@@ -27176,7 +27176,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38">
         <f t="shared" ref="B38:L38" si="1">AVERAGE(B3,B10,B17,B24,B31)</f>
@@ -27225,7 +27225,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <f t="shared" ref="B39:L39" si="2">AVERAGE(B4,B11,B18,B25,B32)</f>
@@ -27274,7 +27274,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40">
         <f t="shared" ref="B40:L40" si="3">AVERAGE(B5,B12,B19,B26,B33)</f>
@@ -27323,7 +27323,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41">
         <f t="shared" ref="B41:L41" si="4">AVERAGE(B6,B13,B20,B27,B34)</f>
@@ -27372,7 +27372,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42">
         <f t="shared" ref="B42:L42" si="5">AVERAGE(B7,B14,B21,B28,B35)</f>
@@ -27468,7 +27468,7 @@
         <v>Скалярный</v>
       </c>
       <c r="B45">
-        <f t="shared" ref="B45:B50" si="7">C30/B30*100</f>
+        <f>C30/B30*100</f>
         <v>23.506866815713831</v>
       </c>
       <c r="D45" s="6">
@@ -27476,45 +27476,45 @@
         <v>20.444444444444443</v>
       </c>
       <c r="E45" s="6">
-        <f t="shared" ref="E45:L45" si="8">E43/E37</f>
+        <f t="shared" ref="E45:L45" si="7">E43/E37</f>
         <v>9.9073001158748557</v>
       </c>
       <c r="F45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20.437037037037037</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20.444444444444443</v>
       </c>
       <c r="H45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>20.481481481481481</v>
       </c>
       <c r="I45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>21.646428571428569</v>
       </c>
       <c r="J45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15.202674227041113</v>
       </c>
       <c r="K45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>10.990802075861778</v>
       </c>
       <c r="L45" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>9.5342675392012417</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <f t="shared" ref="A46:A50" si="9">A38</f>
+        <f t="shared" ref="A46:A50" si="8">A38</f>
         <v>Наивный</v>
       </c>
       <c r="B46">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="B45:B50" si="9">C31/B31*100</f>
         <v>11.508955485733424</v>
       </c>
       <c r="D46" s="6">
@@ -27556,11 +27556,11 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
+        <f t="shared" si="8"/>
+        <v>Скалярный опт.</v>
+      </c>
+      <c r="B47">
         <f t="shared" si="9"/>
-        <v>Скалярный опт.</v>
-      </c>
-      <c r="B47">
-        <f t="shared" si="7"/>
         <v>19.167217448777262</v>
       </c>
       <c r="D47" s="6">
@@ -27602,11 +27602,11 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
+        <f t="shared" si="8"/>
+        <v>SSE</v>
+      </c>
+      <c r="B48">
         <f t="shared" si="9"/>
-        <v>SSE</v>
-      </c>
-      <c r="B48">
-        <f t="shared" si="7"/>
         <v>24.095840867992766</v>
       </c>
       <c r="D48" s="6">
@@ -27648,7 +27648,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>SSE 2</v>
       </c>
       <c r="B49">
@@ -27694,11 +27694,11 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
+        <f t="shared" si="8"/>
+        <v>AVX</v>
+      </c>
+      <c r="B50">
         <f t="shared" si="9"/>
-        <v>AVX</v>
-      </c>
-      <c r="B50">
-        <f t="shared" si="7"/>
         <v>20.917678812415655</v>
       </c>
       <c r="D50" s="6">
